--- a/Backend/ordr_project/media/Generated_RDR1_Sheet.xlsx
+++ b/Backend/ordr_project/media/Generated_RDR1_Sheet.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,8 +520,10 @@
           <t>ZW261910</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>92706</v>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>0092706</t>
+        </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>100</v>
@@ -549,19 +551,19 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MC263005C</t>
+          <t>MC323005N</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0502FA0860N</t>
+          <t>0502FAA03910N</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1760.64</v>
+        <v>2156</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -583,19 +585,19 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>MC323005C</t>
+          <t>MC263005C</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0502FAA01560N</t>
+          <t>0502FA0860N</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>30</v>
+        <v>168</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1918.86</v>
+        <v>1760.63</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -617,17 +619,19 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ZW261910</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>92706</v>
+          <t>MC323005C</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0502FAA01560N</t>
+        </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>753.45</v>
+        <v>1918.86</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -649,17 +653,19 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ZW321910</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>92707</v>
+          <t>MC323005N</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0502FAA03910N</t>
+        </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>835.13</v>
+        <v>2155.99</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -690,7 +696,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1760.64</v>
@@ -715,19 +721,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>MC323005C</t>
+          <t>MC323005N</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0502FAA01560N</t>
+          <t>0502FAA03910N</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1918.86</v>
+        <v>2155.99</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -749,19 +755,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>MT2919KW</t>
+          <t>MC263005C</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0502FAA03040N</t>
+          <t>0502FA0860N</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>972.27</v>
+        <v>1760.64</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -783,17 +789,19 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ZW261910</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>92706</v>
+          <t>MC273005C</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0502FA1160N</t>
+        </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>753.45</v>
+        <v>1771.94</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -815,17 +823,19 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ZW321910</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>92707</v>
+          <t>MC323005N</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0502FAA03910N</t>
+        </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>835.13</v>
+        <v>2155.99</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -847,19 +857,19 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>MC323005N</t>
+          <t>MC263005N</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0502FAA03910N</t>
+          <t>0502FAA03920N</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2156</v>
+        <v>2032.58</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -881,17 +891,19 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ZW261910</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>92706</v>
+          <t>MC263005C</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0502FA0860N</t>
+        </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>753.45</v>
+        <v>1760.64</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -913,17 +925,19 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ZW321910</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>92707</v>
+          <t>MC323005N</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0502FAA03910N</t>
+        </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>835.12</v>
+        <v>2155.99</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -945,17 +959,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ZW321910</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>92707</v>
+          <t>MC323005N</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0502FAA03910N</t>
+        </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>835.13</v>
+        <v>2155.99</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -977,19 +993,19 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>MC263005C</t>
+          <t>MTB414608M</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0502FA0860N</t>
+          <t>7002GAP00020N</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1760.63</v>
+        <v>3416.63</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -997,40 +1013,6 @@
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>FG_FBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>MS293005N</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0502FAA04520N</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>1844.37</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>IGST@28</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>FG_FBD</t>
         </is>
